--- a/SSIS-Project/Timesheets/Teolan/Teolan_Govender_May_FinalWeek.xlsx
+++ b/SSIS-Project/Timesheets/Teolan/Teolan_Govender_May_FinalWeek.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://northerndata-my.sharepoint.com/personal/teolan_govender_sambeconsulting_com/Documents/Documents/Timesheets and Leave/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_TeolanGovender_2026\SSIS-Project\Timesheets\Teolan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1293" documentId="13_ncr:1_{18456319-F974-4A60-AFC5-4E049C41B553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC1D9A93-D9EE-451E-8F6F-8322024E4544}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7A9BA9-6E19-41B1-BB8C-B91FA30DA174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
@@ -2004,13 +2004,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2026,21 +2041,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -7991,7 +7991,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>106</v>
+        <v>212</v>
       </c>
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
@@ -15191,27 +15191,27 @@
       <c r="F7" s="85"/>
     </row>
     <row r="8" spans="1:15" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="138" t="s">
+      <c r="A8" s="135" t="s">
         <v>166</v>
       </c>
-      <c r="B8" s="138"/>
-      <c r="C8" s="138"/>
-      <c r="D8" s="138"/>
-      <c r="E8" s="138"/>
-      <c r="F8" s="138"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="135"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="135"/>
     </row>
     <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="82" t="s">
         <v>170</v>
       </c>
-      <c r="B9" s="141" t="s">
+      <c r="B9" s="132" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="142"/>
-      <c r="D9" s="141" t="s">
+      <c r="C9" s="133"/>
+      <c r="D9" s="132" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="142"/>
+      <c r="E9" s="133"/>
       <c r="F9" s="83" t="s">
         <v>95</v>
       </c>
@@ -15220,103 +15220,103 @@
       <c r="A10" s="78">
         <v>46113</v>
       </c>
-      <c r="B10" s="132" t="s">
+      <c r="B10" s="134" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="132"/>
-      <c r="D10" s="132" t="s">
+      <c r="C10" s="134"/>
+      <c r="D10" s="134" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="132"/>
+      <c r="E10" s="134"/>
       <c r="F10" s="77">
         <v>200</v>
       </c>
-      <c r="G10" s="139" t="s">
+      <c r="G10" s="130" t="s">
         <v>169</v>
       </c>
-      <c r="H10" s="140"/>
-      <c r="I10" s="140"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="140"/>
-      <c r="L10" s="140"/>
-      <c r="M10" s="140"/>
-      <c r="N10" s="140"/>
-      <c r="O10" s="140"/>
+      <c r="H10" s="131"/>
+      <c r="I10" s="131"/>
+      <c r="J10" s="131"/>
+      <c r="K10" s="131"/>
+      <c r="L10" s="131"/>
+      <c r="M10" s="131"/>
+      <c r="N10" s="131"/>
+      <c r="O10" s="131"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="78">
         <v>46113</v>
       </c>
-      <c r="B11" s="130" t="s">
+      <c r="B11" s="136" t="s">
         <v>171</v>
       </c>
-      <c r="C11" s="131"/>
-      <c r="D11" s="132" t="s">
+      <c r="C11" s="137"/>
+      <c r="D11" s="134" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="132"/>
+      <c r="E11" s="134"/>
       <c r="F11" s="77"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="78">
         <v>46113</v>
       </c>
-      <c r="B12" s="130" t="s">
+      <c r="B12" s="136" t="s">
         <v>172</v>
       </c>
-      <c r="C12" s="131"/>
-      <c r="D12" s="132"/>
-      <c r="E12" s="132"/>
+      <c r="C12" s="137"/>
+      <c r="D12" s="134"/>
+      <c r="E12" s="134"/>
       <c r="F12" s="77"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="78">
         <v>46113</v>
       </c>
-      <c r="B13" s="130"/>
-      <c r="C13" s="131"/>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
+      <c r="B13" s="136"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="134"/>
+      <c r="E13" s="134"/>
       <c r="F13" s="77"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="78">
         <v>46113</v>
       </c>
-      <c r="B14" s="130"/>
-      <c r="C14" s="131"/>
-      <c r="D14" s="132"/>
-      <c r="E14" s="132"/>
+      <c r="B14" s="136"/>
+      <c r="C14" s="137"/>
+      <c r="D14" s="134"/>
+      <c r="E14" s="134"/>
       <c r="F14" s="77"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="78">
         <v>46113</v>
       </c>
-      <c r="B15" s="136"/>
-      <c r="C15" s="137"/>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
+      <c r="B15" s="141"/>
+      <c r="C15" s="142"/>
+      <c r="D15" s="134"/>
+      <c r="E15" s="134"/>
       <c r="F15" s="77"/>
     </row>
     <row r="16" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="78">
         <v>46113</v>
       </c>
-      <c r="B16" s="130"/>
-      <c r="C16" s="131"/>
-      <c r="D16" s="132"/>
-      <c r="E16" s="132"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="137"/>
+      <c r="D16" s="134"/>
+      <c r="E16" s="134"/>
       <c r="F16" s="77"/>
     </row>
     <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="133" t="s">
+      <c r="A17" s="138" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="134"/>
-      <c r="C17" s="134"/>
-      <c r="D17" s="134"/>
-      <c r="E17" s="135"/>
+      <c r="B17" s="139"/>
+      <c r="C17" s="139"/>
+      <c r="D17" s="139"/>
+      <c r="E17" s="140"/>
       <c r="F17" s="76">
         <f>SUM(F10:F16)</f>
         <v>200</v>
@@ -15332,16 +15332,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A17:E17"/>
@@ -15351,6 +15341,16 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7 D18" xr:uid="{517DF1E8-3052-48CF-9AE1-C19E6ECB6686}">
@@ -16379,6 +16379,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD10A028B4ACBB47B37340D8D4079B36" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="436e80374471046821afb96e56969fce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="819cb4b524acab89028d2f2d821df341" ns2:_="">
     <xsd:import namespace="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
@@ -16516,15 +16525,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -16532,15 +16532,38 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1863A318-B8F3-4B89-93AD-D5D80D19FCF0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9098A285-2EB1-499B-BF89-1E169B414849}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9098A285-2EB1-499B-BF89-1E169B414849}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1863A318-B8F3-4B89-93AD-D5D80D19FCF0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76F64187-8300-4B72-BC78-4EA8CE42E92D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76F64187-8300-4B72-BC78-4EA8CE42E92D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/SSIS-Project/Timesheets/Teolan/Teolan_Govender_May_FinalWeek.xlsx
+++ b/SSIS-Project/Timesheets/Teolan/Teolan_Govender_May_FinalWeek.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_TeolanGovender_2026\SSIS-Project\Timesheets\Teolan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7A9BA9-6E19-41B1-BB8C-B91FA30DA174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21DA581C-E82F-4E73-97BB-0C511A4B0DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Apr" sheetId="10" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="Key" sheetId="2" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Apr!$A$1:$J$153</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Apr!$A$1:$J$152</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2004,28 +2004,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2041,6 +2026,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3618,7 +3618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B63D3D5-6C83-45F2-B2A7-43EE15BF1EF3}">
-  <dimension ref="A5:J153"/>
+  <dimension ref="A5:J152"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="23" customWidth="1"/>
@@ -3644,7 +3644,7 @@
         <v>93</v>
       </c>
       <c r="B6" s="72">
-        <f>F148</f>
+        <f>F147</f>
         <v>0</v>
       </c>
       <c r="C6" s="37"/>
@@ -5866,7 +5866,7 @@
         <v>224</v>
       </c>
       <c r="H80" s="29">
-        <f t="shared" ref="H80:H115" si="5">J80-I80</f>
+        <f t="shared" ref="H80:H114" si="5">J80-I80</f>
         <v>4.1666666666666741E-2</v>
       </c>
       <c r="I80" s="123">
@@ -5915,18 +5915,37 @@
       <c r="J82" s="35"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A83" s="31"/>
-      <c r="B83" s="31"/>
-      <c r="C83" s="32"/>
-      <c r="D83" s="32"/>
-      <c r="E83" s="32"/>
-      <c r="F83" s="32"/>
-      <c r="G83" s="33"/>
-      <c r="H83" s="34"/>
-      <c r="I83" s="35"/>
-      <c r="J83" s="35"/>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A83" s="22">
+        <v>46132</v>
+      </c>
+      <c r="B83" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D83" s="27"/>
+      <c r="E83" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="F83" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G83" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="H83" s="29">
+        <f t="shared" si="5"/>
+        <v>1.3888888888888895E-2</v>
+      </c>
+      <c r="I83" s="30">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J83" s="30">
+        <v>0.34722222222222221</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A84" s="22">
         <v>46132</v>
       </c>
@@ -5938,26 +5957,26 @@
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="27" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="F84" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G84" s="28" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="H84" s="29">
         <f t="shared" si="5"/>
-        <v>1.3888888888888895E-2</v>
+        <v>0.1076388888888889</v>
       </c>
       <c r="I84" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.34722222222222221</v>
       </c>
       <c r="J84" s="30">
-        <v>0.34722222222222221</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+        <v>0.4548611111111111</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" s="22">
         <v>46132</v>
       </c>
@@ -5969,26 +5988,26 @@
       </c>
       <c r="D85" s="27"/>
       <c r="E85" s="27" t="s">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="F85" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G85" s="28" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="H85" s="29">
         <f t="shared" si="5"/>
-        <v>0.1076388888888889</v>
+        <v>3.4722222222222099E-3</v>
       </c>
       <c r="I85" s="30">
-        <v>0.34722222222222221</v>
+        <v>0.4548611111111111</v>
       </c>
       <c r="J85" s="30">
-        <v>0.4548611111111111</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A86" s="22">
         <v>46132</v>
       </c>
@@ -6000,23 +6019,23 @@
       </c>
       <c r="D86" s="27"/>
       <c r="E86" s="27" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="F86" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G86" s="28" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="H86" s="29">
         <f t="shared" si="5"/>
-        <v>3.4722222222222099E-3</v>
-      </c>
-      <c r="I86" s="30">
-        <v>0.4548611111111111</v>
+        <v>6.2500000000000056E-2</v>
+      </c>
+      <c r="I86" s="123">
+        <v>0.45833333333333331</v>
       </c>
       <c r="J86" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.52083333333333337</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
@@ -6041,13 +6060,13 @@
       </c>
       <c r="H87" s="29">
         <f t="shared" si="5"/>
-        <v>6.2500000000000056E-2</v>
-      </c>
-      <c r="I87" s="123">
-        <v>0.45833333333333331</v>
+        <v>0.10416666666666663</v>
+      </c>
+      <c r="I87" s="30">
+        <v>0.5625</v>
       </c>
       <c r="J87" s="30">
-        <v>0.52083333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
@@ -6062,23 +6081,23 @@
       </c>
       <c r="D88" s="27"/>
       <c r="E88" s="27" t="s">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="F88" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G88" s="28" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H88" s="29">
         <f t="shared" si="5"/>
-        <v>0.10416666666666663</v>
+        <v>2.777777777777779E-2</v>
       </c>
       <c r="I88" s="30">
-        <v>0.5625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J88" s="30">
-        <v>0.66666666666666663</v>
+        <v>0.69444444444444442</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
@@ -6099,25 +6118,25 @@
         <v>15</v>
       </c>
       <c r="G89" s="28" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="H89" s="29">
         <f t="shared" si="5"/>
-        <v>2.777777777777779E-2</v>
+        <v>2.2916666666666696E-2</v>
       </c>
       <c r="I89" s="30">
-        <v>0.66666666666666663</v>
+        <v>0.69444444444444442</v>
       </c>
       <c r="J89" s="30">
-        <v>0.69444444444444442</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+        <v>0.71736111111111112</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" s="22">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B90" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C90" s="27" t="s">
         <v>125</v>
@@ -6130,20 +6149,20 @@
         <v>15</v>
       </c>
       <c r="G90" s="28" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H90" s="29">
         <f t="shared" si="5"/>
-        <v>2.2916666666666696E-2</v>
+        <v>1.388888888888884E-3</v>
       </c>
       <c r="I90" s="30">
-        <v>0.69444444444444442</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J90" s="30">
-        <v>0.71736111111111112</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.3347222222222222</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A91" s="22">
         <v>46133</v>
       </c>
@@ -6155,26 +6174,26 @@
       </c>
       <c r="D91" s="27"/>
       <c r="E91" s="27" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="F91" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G91" s="28" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="H91" s="29">
         <f t="shared" si="5"/>
-        <v>1.388888888888884E-3</v>
+        <v>0.12361111111111112</v>
       </c>
       <c r="I91" s="30">
-        <v>0.33333333333333331</v>
+        <v>0.3347222222222222</v>
       </c>
       <c r="J91" s="30">
-        <v>0.3347222222222222</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" s="22">
         <v>46133</v>
       </c>
@@ -6186,26 +6205,26 @@
       </c>
       <c r="D92" s="27"/>
       <c r="E92" s="27" t="s">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="F92" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G92" s="28" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="H92" s="29">
         <f t="shared" si="5"/>
-        <v>0.12361111111111112</v>
+        <v>4.1666666666666685E-2</v>
       </c>
       <c r="I92" s="30">
-        <v>0.3347222222222222</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J92" s="30">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A93" s="22">
         <v>46133</v>
       </c>
@@ -6217,23 +6236,23 @@
       </c>
       <c r="D93" s="27"/>
       <c r="E93" s="27" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="F93" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G93" s="28" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="H93" s="29">
         <f t="shared" si="5"/>
-        <v>4.1666666666666685E-2</v>
+        <v>2.083333333333337E-2</v>
       </c>
       <c r="I93" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="J93" s="30">
-        <v>0.5</v>
+        <v>0.52083333333333337</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
@@ -6258,13 +6277,13 @@
       </c>
       <c r="H94" s="29">
         <f t="shared" si="5"/>
-        <v>2.083333333333337E-2</v>
-      </c>
-      <c r="I94" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="J94" s="30">
-        <v>0.52083333333333337</v>
+        <v>0.10416666666666663</v>
+      </c>
+      <c r="I94" s="126">
+        <v>0.5625</v>
+      </c>
+      <c r="J94" s="124">
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
@@ -6279,31 +6298,31 @@
       </c>
       <c r="D95" s="27"/>
       <c r="E95" s="27" t="s">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="F95" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G95" s="28" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="H95" s="29">
         <f t="shared" si="5"/>
-        <v>0.10416666666666663</v>
+        <v>4.1666666666666741E-2</v>
       </c>
       <c r="I95" s="126">
-        <v>0.5625</v>
-      </c>
-      <c r="J95" s="124">
         <v>0.66666666666666663</v>
       </c>
-    </row>
-    <row r="96" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="J95" s="30">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" s="22">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B96" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C96" s="27" t="s">
         <v>125</v>
@@ -6316,20 +6335,20 @@
         <v>15</v>
       </c>
       <c r="G96" s="28" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H96" s="29">
         <f t="shared" si="5"/>
-        <v>4.1666666666666741E-2</v>
+        <v>6.9444444444444753E-3</v>
       </c>
       <c r="I96" s="126">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J96" s="30">
-        <v>0.70833333333333337</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J96" s="125">
+        <v>0.34027777777777779</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A97" s="22">
         <v>46134</v>
       </c>
@@ -6341,26 +6360,26 @@
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="27" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="F97" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G97" s="28" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="H97" s="29">
         <f t="shared" si="5"/>
-        <v>6.9444444444444753E-3</v>
-      </c>
-      <c r="I97" s="126">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J97" s="125">
+        <v>0.11805555555555552</v>
+      </c>
+      <c r="I97" s="30">
         <v>0.34027777777777779</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="J97" s="30">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" s="22">
         <v>46134</v>
       </c>
@@ -6372,26 +6391,26 @@
       </c>
       <c r="D98" s="27"/>
       <c r="E98" s="27" t="s">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="F98" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G98" s="28" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="H98" s="29">
         <f t="shared" si="5"/>
-        <v>0.11805555555555552</v>
+        <v>5.2083333333333315E-2</v>
       </c>
       <c r="I98" s="30">
-        <v>0.34027777777777779</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J98" s="30">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.51041666666666663</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A99" s="22">
         <v>46134</v>
       </c>
@@ -6403,23 +6422,23 @@
       </c>
       <c r="D99" s="27"/>
       <c r="E99" s="27" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="F99" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G99" s="28" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="H99" s="29">
         <f t="shared" si="5"/>
-        <v>5.2083333333333315E-2</v>
+        <v>3.125E-2</v>
       </c>
       <c r="I99" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.51041666666666663</v>
       </c>
       <c r="J99" s="30">
-        <v>0.51041666666666663</v>
+        <v>0.54166666666666663</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
@@ -6444,13 +6463,13 @@
       </c>
       <c r="H100" s="29">
         <f t="shared" si="5"/>
-        <v>3.125E-2</v>
+        <v>8.3333333333333259E-2</v>
       </c>
       <c r="I100" s="30">
-        <v>0.51041666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="J100" s="30">
-        <v>0.54166666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
@@ -6465,31 +6484,31 @@
       </c>
       <c r="D101" s="27"/>
       <c r="E101" s="27" t="s">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="F101" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G101" s="28" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="H101" s="29">
         <f t="shared" si="5"/>
-        <v>8.3333333333333259E-2</v>
+        <v>4.1666666666666741E-2</v>
       </c>
       <c r="I101" s="30">
-        <v>0.58333333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J101" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" s="22">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B102" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C102" s="27" t="s">
         <v>125</v>
@@ -6502,20 +6521,20 @@
         <v>15</v>
       </c>
       <c r="G102" s="28" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H102" s="29">
         <f t="shared" si="5"/>
-        <v>4.1666666666666741E-2</v>
-      </c>
-      <c r="I102" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J102" s="30">
-        <v>0.70833333333333337</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+        <v>3.4722222222222654E-3</v>
+      </c>
+      <c r="I102" s="126">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J102" s="125">
+        <v>0.33680555555555558</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A103" s="22">
         <v>46135</v>
       </c>
@@ -6527,26 +6546,26 @@
       </c>
       <c r="D103" s="27"/>
       <c r="E103" s="27" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="F103" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G103" s="28" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="H103" s="29">
         <f t="shared" si="5"/>
-        <v>3.4722222222222654E-3</v>
-      </c>
-      <c r="I103" s="126">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J103" s="125">
+        <v>0.12152777777777773</v>
+      </c>
+      <c r="I103" s="30">
         <v>0.33680555555555558</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="J103" s="30">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" s="22">
         <v>46135</v>
       </c>
@@ -6558,26 +6577,26 @@
       </c>
       <c r="D104" s="27"/>
       <c r="E104" s="27" t="s">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="F104" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G104" s="28" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="H104" s="29">
         <f t="shared" si="5"/>
-        <v>0.12152777777777773</v>
+        <v>4.9305555555555547E-2</v>
       </c>
       <c r="I104" s="30">
-        <v>0.33680555555555558</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J104" s="30">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.50763888888888886</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A105" s="22">
         <v>46135</v>
       </c>
@@ -6589,23 +6608,23 @@
       </c>
       <c r="D105" s="27"/>
       <c r="E105" s="27" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="F105" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G105" s="28" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="H105" s="29">
         <f t="shared" si="5"/>
-        <v>4.9305555555555547E-2</v>
+        <v>1.3194444444444509E-2</v>
       </c>
       <c r="I105" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.50763888888888886</v>
       </c>
       <c r="J105" s="30">
-        <v>0.50763888888888886</v>
+        <v>0.52083333333333337</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
@@ -6630,13 +6649,13 @@
       </c>
       <c r="H106" s="29">
         <f t="shared" si="5"/>
-        <v>1.3194444444444509E-2</v>
+        <v>0.10416666666666663</v>
       </c>
       <c r="I106" s="30">
-        <v>0.50763888888888886</v>
+        <v>0.5625</v>
       </c>
       <c r="J106" s="30">
-        <v>0.52083333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
@@ -6651,31 +6670,31 @@
       </c>
       <c r="D107" s="27"/>
       <c r="E107" s="27" t="s">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="F107" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G107" s="28" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="H107" s="29">
         <f t="shared" si="5"/>
-        <v>0.10416666666666663</v>
+        <v>4.1666666666666741E-2</v>
       </c>
       <c r="I107" s="30">
-        <v>0.5625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J107" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" s="22">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B108" s="22" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C108" s="27" t="s">
         <v>125</v>
@@ -6688,20 +6707,20 @@
         <v>15</v>
       </c>
       <c r="G108" s="28" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H108" s="29">
         <f t="shared" si="5"/>
-        <v>4.1666666666666741E-2</v>
-      </c>
-      <c r="I108" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J108" s="30">
-        <v>0.70833333333333337</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+        <v>9.0277777777778012E-3</v>
+      </c>
+      <c r="I108" s="126">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J108" s="125">
+        <v>0.34236111111111112</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A109" s="22">
         <v>46136</v>
       </c>
@@ -6713,26 +6732,26 @@
       </c>
       <c r="D109" s="27"/>
       <c r="E109" s="27" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="F109" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G109" s="28" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="H109" s="29">
         <f t="shared" si="5"/>
-        <v>9.0277777777778012E-3</v>
-      </c>
-      <c r="I109" s="126">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J109" s="125">
+        <v>0.1159722222222222</v>
+      </c>
+      <c r="I109" s="125">
         <v>0.34236111111111112</v>
       </c>
-    </row>
-    <row r="110" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="J109" s="30">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" s="22">
         <v>46136</v>
       </c>
@@ -6744,26 +6763,26 @@
       </c>
       <c r="D110" s="27"/>
       <c r="E110" s="27" t="s">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="F110" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G110" s="28" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="H110" s="29">
         <f t="shared" si="5"/>
-        <v>0.1159722222222222</v>
-      </c>
-      <c r="I110" s="125">
-        <v>0.34236111111111112</v>
+        <v>3.4722222222222265E-2</v>
+      </c>
+      <c r="I110" s="30">
+        <v>0.45833333333333331</v>
       </c>
       <c r="J110" s="30">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.49305555555555558</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A111" s="22">
         <v>46136</v>
       </c>
@@ -6775,23 +6794,23 @@
       </c>
       <c r="D111" s="27"/>
       <c r="E111" s="27" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="F111" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G111" s="28" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="H111" s="29">
         <f t="shared" si="5"/>
-        <v>3.4722222222222265E-2</v>
+        <v>2.777777777777779E-2</v>
       </c>
       <c r="I111" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.49305555555555558</v>
       </c>
       <c r="J111" s="30">
-        <v>0.49305555555555558</v>
+        <v>0.52083333333333337</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
@@ -6816,13 +6835,13 @@
       </c>
       <c r="H112" s="29">
         <f t="shared" si="5"/>
-        <v>2.777777777777779E-2</v>
+        <v>4.166666666666663E-2</v>
       </c>
       <c r="I112" s="30">
-        <v>0.49305555555555558</v>
-      </c>
-      <c r="J112" s="30">
-        <v>0.52083333333333337</v>
+        <v>0.5625</v>
+      </c>
+      <c r="J112" s="123">
+        <v>0.60416666666666663</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
@@ -6837,23 +6856,23 @@
       </c>
       <c r="D113" s="27"/>
       <c r="E113" s="27" t="s">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="F113" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G113" s="28" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H113" s="29">
         <f t="shared" si="5"/>
-        <v>4.166666666666663E-2</v>
-      </c>
-      <c r="I113" s="30">
-        <v>0.5625</v>
-      </c>
-      <c r="J113" s="123">
+        <v>1.0416666666666741E-2</v>
+      </c>
+      <c r="I113" s="123">
         <v>0.60416666666666663</v>
+      </c>
+      <c r="J113" s="30">
+        <v>0.61458333333333337</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
@@ -6868,23 +6887,23 @@
       </c>
       <c r="D114" s="27"/>
       <c r="E114" s="27" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="F114" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G114" s="28" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H114" s="29">
         <f t="shared" si="5"/>
-        <v>1.0416666666666741E-2</v>
-      </c>
-      <c r="I114" s="123">
-        <v>0.60416666666666663</v>
+        <v>5.2083333333333259E-2</v>
+      </c>
+      <c r="I114" s="30">
+        <v>0.61458333333333337</v>
       </c>
       <c r="J114" s="30">
-        <v>0.61458333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
@@ -6899,62 +6918,50 @@
       </c>
       <c r="D115" s="27"/>
       <c r="E115" s="27" t="s">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="F115" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G115" s="28" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="H115" s="29">
-        <f t="shared" si="5"/>
-        <v>5.2083333333333259E-2</v>
+        <f t="shared" ref="H115:H120" si="6">J115-I115</f>
+        <v>6.25E-2</v>
       </c>
       <c r="I115" s="30">
-        <v>0.61458333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J115" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A116" s="22">
-        <v>46136</v>
-      </c>
-      <c r="B116" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C116" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="D116" s="27"/>
-      <c r="E116" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="F116" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G116" s="28" t="s">
-        <v>224</v>
-      </c>
-      <c r="H116" s="29">
-        <f t="shared" ref="H116:H121" si="6">J116-I116</f>
-        <v>6.25E-2</v>
-      </c>
-      <c r="I116" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J116" s="30">
         <v>0.72916666666666663</v>
       </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A116" s="31">
+        <v>46137</v>
+      </c>
+      <c r="B116" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C116" s="32"/>
+      <c r="D116" s="32"/>
+      <c r="E116" s="32"/>
+      <c r="F116" s="32"/>
+      <c r="G116" s="33"/>
+      <c r="H116" s="34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I116" s="35"/>
+      <c r="J116" s="35"/>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" s="31">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B117" s="31" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C117" s="32"/>
       <c r="D117" s="32"/>
@@ -6969,56 +6976,68 @@
       <c r="J117" s="35"/>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A118" s="31">
-        <v>46138</v>
-      </c>
-      <c r="B118" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" s="32"/>
-      <c r="D118" s="32"/>
-      <c r="E118" s="32"/>
-      <c r="F118" s="32"/>
-      <c r="G118" s="33"/>
-      <c r="H118" s="34">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I118" s="35"/>
-      <c r="J118" s="35"/>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A119" s="47">
+      <c r="A118" s="47">
         <v>46139</v>
       </c>
-      <c r="B119" s="47" t="s">
+      <c r="B118" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="C119" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="D119" s="48"/>
-      <c r="E119" s="48" t="s">
+      <c r="C118" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="D118" s="48"/>
+      <c r="E118" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="F119" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="G119" s="49" t="s">
+      <c r="F118" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="G118" s="49" t="s">
         <v>179</v>
       </c>
-      <c r="H119" s="50">
+      <c r="H118" s="50">
         <f t="shared" si="6"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="I119" s="51">
+      <c r="I118" s="51">
         <v>0.33333333333333331</v>
       </c>
-      <c r="J119" s="51">
+      <c r="J118" s="51">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A119" s="22">
+        <v>46140</v>
+      </c>
+      <c r="B119" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C119" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D119" s="27"/>
+      <c r="E119" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="F119" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G119" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="H119" s="29">
+        <f t="shared" si="6"/>
+        <v>4.1666666666667074E-3</v>
+      </c>
+      <c r="I119" s="126">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J119" s="30">
+        <v>0.33750000000000002</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A120" s="22">
         <v>46140</v>
       </c>
@@ -7030,26 +7049,26 @@
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="27" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="F120" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G120" s="28" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="H120" s="29">
         <f t="shared" si="6"/>
-        <v>4.1666666666667074E-3</v>
-      </c>
-      <c r="I120" s="126">
-        <v>0.33333333333333331</v>
+        <v>0.12083333333333329</v>
+      </c>
+      <c r="I120" s="30">
+        <v>0.33750000000000002</v>
       </c>
       <c r="J120" s="30">
-        <v>0.33750000000000002</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="22">
         <v>46140</v>
       </c>
@@ -7061,23 +7080,23 @@
       </c>
       <c r="D121" s="27"/>
       <c r="E121" s="27" t="s">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="F121" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G121" s="28" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="H121" s="29">
-        <f t="shared" si="6"/>
-        <v>0.12083333333333329</v>
+        <f>J121-I121</f>
+        <v>4.3055555555555569E-2</v>
       </c>
       <c r="I121" s="30">
-        <v>0.33750000000000002</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J121" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.50138888888888888</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.2">
@@ -7092,80 +7111,80 @@
       </c>
       <c r="D122" s="27"/>
       <c r="E122" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="F122" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G122" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="H122" s="29">
+        <f t="shared" ref="H122:H125" si="7">J122-I122</f>
+        <v>2.2916666666666696E-2</v>
+      </c>
+      <c r="I122" s="30">
+        <v>0.50138888888888888</v>
+      </c>
+      <c r="J122" s="30">
+        <v>0.52430555555555558</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A123" s="22"/>
+      <c r="B123" s="22"/>
+      <c r="C123" s="27"/>
+      <c r="D123" s="27"/>
+      <c r="E123" s="27"/>
+      <c r="F123" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G123" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="H123" s="29">
+        <f t="shared" si="7"/>
+        <v>3.819444444444442E-2</v>
+      </c>
+      <c r="I123" s="30">
+        <v>0.56597222222222221</v>
+      </c>
+      <c r="J123" s="30">
+        <v>0.60416666666666663</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A124" s="22">
+        <v>46140</v>
+      </c>
+      <c r="B124" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C124" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D124" s="27"/>
+      <c r="E124" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="F122" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G122" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="H122" s="29">
-        <f>J122-I122</f>
-        <v>4.3055555555555569E-2</v>
-      </c>
-      <c r="I122" s="30">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="J122" s="30">
-        <v>0.50138888888888888</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A123" s="22">
-        <v>46140</v>
-      </c>
-      <c r="B123" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C123" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="D123" s="27"/>
-      <c r="E123" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="F123" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G123" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="H123" s="29">
-        <f t="shared" ref="H123:H126" si="7">J123-I123</f>
-        <v>2.2916666666666696E-2</v>
-      </c>
-      <c r="I123" s="30">
-        <v>0.50138888888888888</v>
-      </c>
-      <c r="J123" s="30">
-        <v>0.52430555555555558</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A124" s="22"/>
-      <c r="B124" s="22"/>
-      <c r="C124" s="27"/>
-      <c r="D124" s="27"/>
-      <c r="E124" s="27"/>
       <c r="F124" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G124" s="28" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="H124" s="29">
         <f t="shared" si="7"/>
-        <v>3.819444444444442E-2</v>
+        <v>4.1666666666666741E-2</v>
       </c>
       <c r="I124" s="30">
-        <v>0.56597222222222221</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="J124" s="30">
-        <v>0.60416666666666663</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="22">
         <v>46140</v>
       </c>
@@ -7177,26 +7196,26 @@
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="27" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F125" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G125" s="28" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="H125" s="29">
         <f t="shared" si="7"/>
-        <v>4.1666666666666741E-2</v>
+        <v>2.0833333333333259E-2</v>
       </c>
       <c r="I125" s="30">
-        <v>0.60416666666666663</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="J125" s="30">
-        <v>0.64583333333333337</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A126" s="22">
         <v>46140</v>
       </c>
@@ -7208,26 +7227,26 @@
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="27" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F126" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G126" s="28" t="s">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="H126" s="29">
-        <f t="shared" si="7"/>
-        <v>2.0833333333333259E-2</v>
+        <f>J126-I126</f>
+        <v>3.5416666666666652E-2</v>
       </c>
       <c r="I126" s="30">
-        <v>0.64583333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J126" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+        <v>0.70208333333333328</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" s="22">
         <v>46140</v>
       </c>
@@ -7245,25 +7264,25 @@
         <v>15</v>
       </c>
       <c r="G127" s="28" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="H127" s="29">
         <f>J127-I127</f>
-        <v>3.5416666666666652E-2</v>
+        <v>2.7083333333333348E-2</v>
       </c>
       <c r="I127" s="30">
-        <v>0.66666666666666663</v>
+        <v>0.70208333333333328</v>
       </c>
       <c r="J127" s="30">
-        <v>0.70208333333333328</v>
+        <v>0.72916666666666663</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="22">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B128" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C128" s="27" t="s">
         <v>125</v>
@@ -7276,17 +7295,17 @@
         <v>15</v>
       </c>
       <c r="G128" s="28" t="s">
-        <v>256</v>
+        <v>222</v>
       </c>
       <c r="H128" s="29">
-        <f>J128-I128</f>
-        <v>2.7083333333333348E-2</v>
-      </c>
-      <c r="I128" s="30">
-        <v>0.70208333333333328</v>
-      </c>
-      <c r="J128" s="30">
-        <v>0.72916666666666663</v>
+        <f t="shared" ref="H128:H142" si="8">J128-I128</f>
+        <v>1.3888888888888895E-2</v>
+      </c>
+      <c r="I128" s="126">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J128" s="126">
+        <v>0.34722222222222221</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.2">
@@ -7306,18 +7325,18 @@
       <c r="F129" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G129" s="28" t="s">
-        <v>222</v>
+      <c r="G129" s="127" t="s">
+        <v>255</v>
       </c>
       <c r="H129" s="29">
-        <f t="shared" ref="H129:H143" si="8">J129-I129</f>
-        <v>1.3888888888888895E-2</v>
+        <f t="shared" si="8"/>
+        <v>2.9166666666666674E-2</v>
       </c>
       <c r="I129" s="126">
-        <v>0.33333333333333331</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="J129" s="126">
-        <v>0.34722222222222221</v>
+        <v>0.38333333333333336</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.2">
@@ -7332,26 +7351,26 @@
       </c>
       <c r="D130" s="27"/>
       <c r="E130" s="27" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="F130" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G130" s="127" t="s">
-        <v>255</v>
+      <c r="G130" s="23" t="s">
+        <v>258</v>
       </c>
       <c r="H130" s="29">
         <f t="shared" si="8"/>
-        <v>2.9166666666666674E-2</v>
+        <v>1.2499999999999956E-2</v>
       </c>
       <c r="I130" s="126">
-        <v>0.35416666666666669</v>
+        <v>0.38333333333333336</v>
       </c>
       <c r="J130" s="126">
-        <v>0.38333333333333336</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.39583333333333331</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A131" s="22">
         <v>46141</v>
       </c>
@@ -7363,26 +7382,26 @@
       </c>
       <c r="D131" s="27"/>
       <c r="E131" s="27" t="s">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="F131" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G131" s="23" t="s">
-        <v>258</v>
+      <c r="G131" s="28" t="s">
+        <v>259</v>
       </c>
       <c r="H131" s="29">
         <f t="shared" si="8"/>
-        <v>1.2499999999999956E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="I131" s="126">
-        <v>0.38333333333333336</v>
-      </c>
-      <c r="J131" s="126">
         <v>0.39583333333333331</v>
       </c>
-    </row>
-    <row r="132" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="J131" s="30">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="22">
         <v>46141</v>
       </c>
@@ -7400,17 +7419,17 @@
         <v>15</v>
       </c>
       <c r="G132" s="28" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="H132" s="29">
         <f t="shared" si="8"/>
-        <v>6.25E-2</v>
-      </c>
-      <c r="I132" s="126">
-        <v>0.39583333333333331</v>
+        <v>3.3333333333333326E-2</v>
+      </c>
+      <c r="I132" s="30">
+        <v>0.45833333333333331</v>
       </c>
       <c r="J132" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.49166666666666664</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.2">
@@ -7425,26 +7444,26 @@
       </c>
       <c r="D133" s="27"/>
       <c r="E133" s="27" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="F133" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G133" s="28" t="s">
-        <v>223</v>
+      <c r="G133" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="H133" s="29">
         <f t="shared" si="8"/>
-        <v>3.3333333333333326E-2</v>
+        <v>3.2638888888888939E-2</v>
       </c>
       <c r="I133" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.49166666666666664</v>
       </c>
       <c r="J133" s="30">
-        <v>0.49166666666666664</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.52430555555555558</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A134" s="22">
         <v>46141</v>
       </c>
@@ -7461,18 +7480,18 @@
       <c r="F134" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G134" s="23" t="s">
-        <v>260</v>
+      <c r="G134" s="28" t="s">
+        <v>261</v>
       </c>
       <c r="H134" s="29">
         <f t="shared" si="8"/>
-        <v>3.2638888888888939E-2</v>
+        <v>0.10069444444444442</v>
       </c>
       <c r="I134" s="30">
-        <v>0.49166666666666664</v>
+        <v>0.56597222222222221</v>
       </c>
       <c r="J134" s="30">
-        <v>0.52430555555555558</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="135" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
@@ -7487,31 +7506,31 @@
       </c>
       <c r="D135" s="27"/>
       <c r="E135" s="27" t="s">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="F135" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G135" s="28" t="s">
-        <v>261</v>
+        <v>224</v>
       </c>
       <c r="H135" s="29">
         <f t="shared" si="8"/>
-        <v>0.10069444444444442</v>
+        <v>4.4444444444444509E-2</v>
       </c>
       <c r="I135" s="30">
-        <v>0.56597222222222221</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J135" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+        <v>0.71111111111111114</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="22">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B136" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C136" s="27" t="s">
         <v>125</v>
@@ -7524,17 +7543,17 @@
         <v>15</v>
       </c>
       <c r="G136" s="28" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H136" s="29">
         <f t="shared" si="8"/>
-        <v>4.4444444444444509E-2</v>
-      </c>
-      <c r="I136" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J136" s="30">
-        <v>0.71111111111111114</v>
+        <v>1.3888888888888895E-2</v>
+      </c>
+      <c r="I136" s="126">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J136" s="126">
+        <v>0.34722222222222221</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.2">
@@ -7549,23 +7568,23 @@
       </c>
       <c r="D137" s="27"/>
       <c r="E137" s="27" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="F137" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G137" s="28" t="s">
-        <v>222</v>
+      <c r="G137" s="23" t="s">
+        <v>252</v>
       </c>
       <c r="H137" s="29">
         <f t="shared" si="8"/>
-        <v>1.3888888888888895E-2</v>
+        <v>6.9444444444444475E-2</v>
       </c>
       <c r="I137" s="126">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J137" s="126">
         <v>0.34722222222222221</v>
+      </c>
+      <c r="J137" s="30">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.2">
@@ -7580,26 +7599,26 @@
       </c>
       <c r="D138" s="27"/>
       <c r="E138" s="27" t="s">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="F138" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G138" s="23" t="s">
-        <v>252</v>
+      <c r="G138" s="28" t="s">
+        <v>223</v>
       </c>
       <c r="H138" s="29">
         <f t="shared" si="8"/>
-        <v>6.9444444444444475E-2</v>
-      </c>
-      <c r="I138" s="126">
-        <v>0.34722222222222221</v>
+        <v>4.166666666666663E-2</v>
+      </c>
+      <c r="I138" s="30">
+        <v>0.41666666666666669</v>
       </c>
       <c r="J138" s="30">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A139" s="22">
         <v>46142</v>
       </c>
@@ -7611,23 +7630,23 @@
       </c>
       <c r="D139" s="27"/>
       <c r="E139" s="27" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F139" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G139" s="28" t="s">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="H139" s="29">
         <f t="shared" si="8"/>
-        <v>4.166666666666663E-2</v>
+        <v>6.2500000000000056E-2</v>
       </c>
       <c r="I139" s="30">
-        <v>0.41666666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J139" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.52083333333333337</v>
       </c>
     </row>
     <row r="140" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
@@ -7642,23 +7661,23 @@
       </c>
       <c r="D140" s="27"/>
       <c r="E140" s="27" t="s">
-        <v>64</v>
+        <v>221</v>
       </c>
       <c r="F140" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G140" s="28" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="H140" s="29">
         <f t="shared" si="8"/>
-        <v>6.2500000000000056E-2</v>
+        <v>4.166666666666663E-2</v>
       </c>
       <c r="I140" s="30">
-        <v>0.45833333333333331</v>
+        <v>0.5625</v>
       </c>
       <c r="J140" s="30">
-        <v>0.52083333333333337</v>
+        <v>0.60416666666666663</v>
       </c>
     </row>
     <row r="141" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
@@ -7673,23 +7692,23 @@
       </c>
       <c r="D141" s="27"/>
       <c r="E141" s="27" t="s">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="F141" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G141" s="28" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H141" s="29">
         <f t="shared" si="8"/>
-        <v>4.166666666666663E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="I141" s="30">
-        <v>0.5625</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="J141" s="30">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="142" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
@@ -7710,137 +7729,115 @@
         <v>15</v>
       </c>
       <c r="G142" s="28" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="H142" s="29">
         <f t="shared" si="8"/>
-        <v>6.25E-2</v>
+        <v>5.4861111111111138E-2</v>
       </c>
       <c r="I142" s="30">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J142" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A143" s="22">
-        <v>46142</v>
-      </c>
-      <c r="B143" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C143" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="D143" s="27"/>
-      <c r="E143" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="F143" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G143" s="28" t="s">
-        <v>257</v>
-      </c>
-      <c r="H143" s="29">
-        <f t="shared" si="8"/>
-        <v>5.4861111111111138E-2</v>
-      </c>
-      <c r="I143" s="30">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J143" s="30">
         <v>0.72152777777777777</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="46"/>
-      <c r="B144" s="46"/>
-      <c r="G144" s="40"/>
-      <c r="H144" s="64"/>
-      <c r="I144" s="65"/>
-      <c r="J144" s="65"/>
-    </row>
-    <row r="145" spans="1:8" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="46"/>
+      <c r="B143" s="46"/>
+      <c r="G143" s="40"/>
+      <c r="H143" s="64"/>
+      <c r="I143" s="65"/>
+      <c r="J143" s="65"/>
+    </row>
+    <row r="144" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="4"/>
+      <c r="B144" s="4"/>
+      <c r="C144" s="5"/>
+      <c r="D144" s="6"/>
+      <c r="E144" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F144" s="8">
+        <v>152</v>
+      </c>
+      <c r="H144" s="40"/>
+    </row>
+    <row r="145" spans="1:8" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
-      <c r="C145" s="5"/>
-      <c r="D145" s="6"/>
-      <c r="E145" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F145" s="8">
-        <v>152</v>
+      <c r="C145" s="9"/>
+      <c r="D145" s="2"/>
+      <c r="E145" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F145" s="11">
+        <v>19</v>
       </c>
       <c r="H145" s="40"/>
     </row>
     <row r="146" spans="1:8" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="4"/>
-      <c r="B146" s="4"/>
-      <c r="C146" s="9"/>
-      <c r="D146" s="2"/>
-      <c r="E146" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F146" s="11">
-        <v>19</v>
-      </c>
+      <c r="A146" s="128" t="s">
+        <v>23</v>
+      </c>
+      <c r="B146" s="128"/>
+      <c r="C146" s="128"/>
+      <c r="D146" s="12"/>
+      <c r="E146" s="2"/>
+      <c r="F146" s="2"/>
       <c r="H146" s="40"/>
     </row>
-    <row r="147" spans="1:8" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="128" t="s">
-        <v>23</v>
-      </c>
-      <c r="B147" s="128"/>
-      <c r="C147" s="128"/>
-      <c r="D147" s="12"/>
-      <c r="E147" s="2"/>
-      <c r="F147" s="2"/>
-      <c r="H147" s="40"/>
-    </row>
-    <row r="148" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A148" s="13"/>
-      <c r="B148" s="13"/>
-      <c r="C148" s="6"/>
-      <c r="D148" s="6"/>
-      <c r="E148" s="14" t="s">
+    <row r="147" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A147" s="13"/>
+      <c r="B147" s="13"/>
+      <c r="C147" s="6"/>
+      <c r="D147" s="6"/>
+      <c r="E147" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F148" s="15">
-        <f>SUMIF(F9:F143,"Billable",H9:H143)</f>
+      <c r="F147" s="15">
+        <f>SUMIF(F9:F142,"Billable",H9:H142)</f>
         <v>0</v>
       </c>
-      <c r="H148" s="38"/>
-    </row>
-    <row r="149" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="129" t="s">
+      <c r="H147" s="38"/>
+    </row>
+    <row r="148" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="129" t="s">
         <v>25</v>
       </c>
-      <c r="B149" s="129"/>
-      <c r="C149" s="129"/>
-      <c r="D149" s="16"/>
-      <c r="E149" s="17" t="s">
+      <c r="B148" s="129"/>
+      <c r="C148" s="129"/>
+      <c r="D148" s="16"/>
+      <c r="E148" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="F149" s="18">
-        <f>SUMIF(F9:F143,"Non-Billable",H9:H143)</f>
+      <c r="F148" s="18">
+        <f>SUMIF(F9:F142,"Non-Billable",H9:H142)</f>
         <v>7.2666666666666719</v>
       </c>
+      <c r="H148" s="40"/>
+    </row>
+    <row r="149" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="2"/>
+      <c r="B149" s="2"/>
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
+      <c r="E149" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F149" s="44">
+        <f>F147+F148</f>
+        <v>7.2666666666666719</v>
+      </c>
       <c r="H149" s="40"/>
     </row>
-    <row r="150" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
-      <c r="E150" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="F150" s="44">
-        <f>F148+F149</f>
-        <v>7.2666666666666719</v>
-      </c>
+      <c r="E150" s="2"/>
+      <c r="F150" s="2"/>
       <c r="H150" s="40"/>
     </row>
     <row r="151" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7848,29 +7845,20 @@
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
-      <c r="E151" s="2"/>
-      <c r="F151" s="2"/>
+      <c r="E151" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F151" s="21"/>
       <c r="H151" s="40"/>
     </row>
     <row r="152" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="2"/>
-      <c r="B152" s="2"/>
-      <c r="C152" s="2"/>
-      <c r="D152" s="2"/>
-      <c r="E152" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="F152" s="21"/>
+      <c r="E152" s="39"/>
       <c r="H152" s="40"/>
-    </row>
-    <row r="153" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E153" s="39"/>
-      <c r="H153" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A147:C147"/>
-    <mergeCell ref="A149:C149"/>
+    <mergeCell ref="A146:C146"/>
+    <mergeCell ref="A148:C148"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A6:B6 D7:E7">
@@ -7896,7 +7884,7 @@
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8:B153">
+  <conditionalFormatting sqref="B8:B152">
     <cfRule type="containsText" dxfId="88" priority="1" operator="containsText" text="Saturday">
       <formula>NOT(ISERROR(SEARCH("Saturday",B8)))</formula>
     </cfRule>
@@ -7904,31 +7892,31 @@
       <formula>NOT(ISERROR(SEARCH("Sunday",B8)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D145:E145 D147:E149 E152">
+  <conditionalFormatting sqref="D144:E144 D146:E148 E151">
     <cfRule type="containsText" dxfId="86" priority="3" operator="containsText" text="Religious Leave">
-      <formula>NOT(ISERROR(SEARCH("Religious Leave",D145)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Religious Leave",D144)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="85" priority="4" operator="containsText" text="Birthday Leave">
-      <formula>NOT(ISERROR(SEARCH("Birthday Leave",D145)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Birthday Leave",D144)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="84" priority="5" operator="containsText" text="Study Leave">
-      <formula>NOT(ISERROR(SEARCH("Study Leave",D145)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Study Leave",D144)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="83" priority="6" operator="containsText" text="Family Responsibility Leave">
-      <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D145)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Family Responsibility Leave",D144)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="82" priority="7" operator="containsText" text="Sick Leave">
-      <formula>NOT(ISERROR(SEARCH("Sick Leave",D145)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Sick Leave",D144)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="81" priority="8" operator="containsText" text="Annual Leave">
-      <formula>NOT(ISERROR(SEARCH("Annual Leave",D145)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Annual Leave",D144)))</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="80" priority="9" operator="equal">
       <formula>"Public Holiday"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="time" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Time Format" error="Please input a valid time. For e.g. 08:00" sqref="I9:J53 J54 I55:J66 J68 I69:J72 J74 I75:J78 I81:I86 J80:J87 I88:J94 J96 I98:J102 I104:J108 J110:J112 I111:I113 I115:I119 I139:J144 J132 I121:I128 I133:J136 J138 J114:J128" xr:uid="{68437EC4-DD9C-463B-9F8D-7339DE1FDE4C}">
+    <dataValidation type="time" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Time Format" error="Please input a valid time. For e.g. 08:00" sqref="I9:J53 J54 I55:J66 J68 I69:J72 J74 I75:J78 I87:J93 J95 I97:J101 I103:J107 J109:J111 I110:I112 I114:I118 I138:J143 J131 I120:I127 I132:J135 J137 J113:J127 J80:J86 I81:I85" xr:uid="{68437EC4-DD9C-463B-9F8D-7339DE1FDE4C}">
       <formula1>0</formula1>
       <formula2>0.999988425925926</formula2>
     </dataValidation>
@@ -7936,7 +7924,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="35" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="116" max="9" man="1"/>
+    <brk id="115" max="9" man="1"/>
   </rowBreaks>
   <drawing r:id="rId2"/>
   <extLst>
@@ -7952,19 +7940,19 @@
           <x14:formula1>
             <xm:f>Key!$B$2:$B$54</xm:f>
           </x14:formula1>
-          <xm:sqref>C9:C144</xm:sqref>
+          <xm:sqref>C9:C143</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D3F3BEC1-F54D-4034-9200-E177F5F22F68}">
           <x14:formula1>
             <xm:f>Key!$J$3:$J$4</xm:f>
           </x14:formula1>
-          <xm:sqref>F9:F144</xm:sqref>
+          <xm:sqref>F9:F143</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8D174978-0CE3-4483-935A-E2D2B6171911}">
           <x14:formula1>
             <xm:f>Key!$F$3:$F$47</xm:f>
           </x14:formula1>
-          <xm:sqref>E9:E144</xm:sqref>
+          <xm:sqref>E9:E143</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -15191,27 +15179,27 @@
       <c r="F7" s="85"/>
     </row>
     <row r="8" spans="1:15" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="135" t="s">
+      <c r="A8" s="138" t="s">
         <v>166</v>
       </c>
-      <c r="B8" s="135"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="135"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="135"/>
+      <c r="B8" s="138"/>
+      <c r="C8" s="138"/>
+      <c r="D8" s="138"/>
+      <c r="E8" s="138"/>
+      <c r="F8" s="138"/>
     </row>
     <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="82" t="s">
         <v>170</v>
       </c>
-      <c r="B9" s="132" t="s">
+      <c r="B9" s="141" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="133"/>
-      <c r="D9" s="132" t="s">
+      <c r="C9" s="142"/>
+      <c r="D9" s="141" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="133"/>
+      <c r="E9" s="142"/>
       <c r="F9" s="83" t="s">
         <v>95</v>
       </c>
@@ -15220,103 +15208,103 @@
       <c r="A10" s="78">
         <v>46113</v>
       </c>
-      <c r="B10" s="134" t="s">
+      <c r="B10" s="132" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="134"/>
-      <c r="D10" s="134" t="s">
+      <c r="C10" s="132"/>
+      <c r="D10" s="132" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="134"/>
+      <c r="E10" s="132"/>
       <c r="F10" s="77">
         <v>200</v>
       </c>
-      <c r="G10" s="130" t="s">
+      <c r="G10" s="139" t="s">
         <v>169</v>
       </c>
-      <c r="H10" s="131"/>
-      <c r="I10" s="131"/>
-      <c r="J10" s="131"/>
-      <c r="K10" s="131"/>
-      <c r="L10" s="131"/>
-      <c r="M10" s="131"/>
-      <c r="N10" s="131"/>
-      <c r="O10" s="131"/>
+      <c r="H10" s="140"/>
+      <c r="I10" s="140"/>
+      <c r="J10" s="140"/>
+      <c r="K10" s="140"/>
+      <c r="L10" s="140"/>
+      <c r="M10" s="140"/>
+      <c r="N10" s="140"/>
+      <c r="O10" s="140"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="78">
         <v>46113</v>
       </c>
-      <c r="B11" s="136" t="s">
+      <c r="B11" s="130" t="s">
         <v>171</v>
       </c>
-      <c r="C11" s="137"/>
-      <c r="D11" s="134" t="s">
+      <c r="C11" s="131"/>
+      <c r="D11" s="132" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="134"/>
+      <c r="E11" s="132"/>
       <c r="F11" s="77"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="78">
         <v>46113</v>
       </c>
-      <c r="B12" s="136" t="s">
+      <c r="B12" s="130" t="s">
         <v>172</v>
       </c>
-      <c r="C12" s="137"/>
-      <c r="D12" s="134"/>
-      <c r="E12" s="134"/>
+      <c r="C12" s="131"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
       <c r="F12" s="77"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="78">
         <v>46113</v>
       </c>
-      <c r="B13" s="136"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="134"/>
-      <c r="E13" s="134"/>
+      <c r="B13" s="130"/>
+      <c r="C13" s="131"/>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
       <c r="F13" s="77"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="78">
         <v>46113</v>
       </c>
-      <c r="B14" s="136"/>
-      <c r="C14" s="137"/>
-      <c r="D14" s="134"/>
-      <c r="E14" s="134"/>
+      <c r="B14" s="130"/>
+      <c r="C14" s="131"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
       <c r="F14" s="77"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="78">
         <v>46113</v>
       </c>
-      <c r="B15" s="141"/>
-      <c r="C15" s="142"/>
-      <c r="D15" s="134"/>
-      <c r="E15" s="134"/>
+      <c r="B15" s="136"/>
+      <c r="C15" s="137"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
       <c r="F15" s="77"/>
     </row>
     <row r="16" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="78">
         <v>46113</v>
       </c>
-      <c r="B16" s="136"/>
-      <c r="C16" s="137"/>
-      <c r="D16" s="134"/>
-      <c r="E16" s="134"/>
+      <c r="B16" s="130"/>
+      <c r="C16" s="131"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
       <c r="F16" s="77"/>
     </row>
     <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="138" t="s">
+      <c r="A17" s="133" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="139"/>
-      <c r="C17" s="139"/>
-      <c r="D17" s="139"/>
-      <c r="E17" s="140"/>
+      <c r="B17" s="134"/>
+      <c r="C17" s="134"/>
+      <c r="D17" s="134"/>
+      <c r="E17" s="135"/>
       <c r="F17" s="76">
         <f>SUM(F10:F16)</f>
         <v>200</v>
@@ -15332,6 +15320,16 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A17:E17"/>
@@ -15341,16 +15339,6 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7 D18" xr:uid="{517DF1E8-3052-48CF-9AE1-C19E6ECB6686}">
@@ -16379,12 +16367,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16526,15 +16511,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9098A285-2EB1-499B-BF89-1E169B414849}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76F64187-8300-4B72-BC78-4EA8CE42E92D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -16558,10 +16547,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76F64187-8300-4B72-BC78-4EA8CE42E92D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9098A285-2EB1-499B-BF89-1E169B414849}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/SSIS-Project/Timesheets/Teolan/Teolan_Govender_May_FinalWeek.xlsx
+++ b/SSIS-Project/Timesheets/Teolan/Teolan_Govender_May_FinalWeek.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_TeolanGovender_2026\SSIS-Project\Timesheets\Teolan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21DA581C-E82F-4E73-97BB-0C511A4B0DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F678BE1-E04F-47EB-9881-DC92B3DD7F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Apr" sheetId="10" r:id="rId1"/>
@@ -2004,13 +2004,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2026,21 +2041,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3016,7 +3016,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1953195" cy="601132"/>
+          <a:ext cx="1954253" cy="578907"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -15179,27 +15179,27 @@
       <c r="F7" s="85"/>
     </row>
     <row r="8" spans="1:15" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="138" t="s">
+      <c r="A8" s="135" t="s">
         <v>166</v>
       </c>
-      <c r="B8" s="138"/>
-      <c r="C8" s="138"/>
-      <c r="D8" s="138"/>
-      <c r="E8" s="138"/>
-      <c r="F8" s="138"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="135"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="135"/>
     </row>
     <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="82" t="s">
         <v>170</v>
       </c>
-      <c r="B9" s="141" t="s">
+      <c r="B9" s="132" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="142"/>
-      <c r="D9" s="141" t="s">
+      <c r="C9" s="133"/>
+      <c r="D9" s="132" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="142"/>
+      <c r="E9" s="133"/>
       <c r="F9" s="83" t="s">
         <v>95</v>
       </c>
@@ -15208,103 +15208,103 @@
       <c r="A10" s="78">
         <v>46113</v>
       </c>
-      <c r="B10" s="132" t="s">
+      <c r="B10" s="134" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="132"/>
-      <c r="D10" s="132" t="s">
+      <c r="C10" s="134"/>
+      <c r="D10" s="134" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="132"/>
+      <c r="E10" s="134"/>
       <c r="F10" s="77">
         <v>200</v>
       </c>
-      <c r="G10" s="139" t="s">
+      <c r="G10" s="130" t="s">
         <v>169</v>
       </c>
-      <c r="H10" s="140"/>
-      <c r="I10" s="140"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="140"/>
-      <c r="L10" s="140"/>
-      <c r="M10" s="140"/>
-      <c r="N10" s="140"/>
-      <c r="O10" s="140"/>
+      <c r="H10" s="131"/>
+      <c r="I10" s="131"/>
+      <c r="J10" s="131"/>
+      <c r="K10" s="131"/>
+      <c r="L10" s="131"/>
+      <c r="M10" s="131"/>
+      <c r="N10" s="131"/>
+      <c r="O10" s="131"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="78">
         <v>46113</v>
       </c>
-      <c r="B11" s="130" t="s">
+      <c r="B11" s="136" t="s">
         <v>171</v>
       </c>
-      <c r="C11" s="131"/>
-      <c r="D11" s="132" t="s">
+      <c r="C11" s="137"/>
+      <c r="D11" s="134" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="132"/>
+      <c r="E11" s="134"/>
       <c r="F11" s="77"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="78">
         <v>46113</v>
       </c>
-      <c r="B12" s="130" t="s">
+      <c r="B12" s="136" t="s">
         <v>172</v>
       </c>
-      <c r="C12" s="131"/>
-      <c r="D12" s="132"/>
-      <c r="E12" s="132"/>
+      <c r="C12" s="137"/>
+      <c r="D12" s="134"/>
+      <c r="E12" s="134"/>
       <c r="F12" s="77"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="78">
         <v>46113</v>
       </c>
-      <c r="B13" s="130"/>
-      <c r="C13" s="131"/>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
+      <c r="B13" s="136"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="134"/>
+      <c r="E13" s="134"/>
       <c r="F13" s="77"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="78">
         <v>46113</v>
       </c>
-      <c r="B14" s="130"/>
-      <c r="C14" s="131"/>
-      <c r="D14" s="132"/>
-      <c r="E14" s="132"/>
+      <c r="B14" s="136"/>
+      <c r="C14" s="137"/>
+      <c r="D14" s="134"/>
+      <c r="E14" s="134"/>
       <c r="F14" s="77"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="78">
         <v>46113</v>
       </c>
-      <c r="B15" s="136"/>
-      <c r="C15" s="137"/>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
+      <c r="B15" s="141"/>
+      <c r="C15" s="142"/>
+      <c r="D15" s="134"/>
+      <c r="E15" s="134"/>
       <c r="F15" s="77"/>
     </row>
     <row r="16" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="78">
         <v>46113</v>
       </c>
-      <c r="B16" s="130"/>
-      <c r="C16" s="131"/>
-      <c r="D16" s="132"/>
-      <c r="E16" s="132"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="137"/>
+      <c r="D16" s="134"/>
+      <c r="E16" s="134"/>
       <c r="F16" s="77"/>
     </row>
     <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="133" t="s">
+      <c r="A17" s="138" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="134"/>
-      <c r="C17" s="134"/>
-      <c r="D17" s="134"/>
-      <c r="E17" s="135"/>
+      <c r="B17" s="139"/>
+      <c r="C17" s="139"/>
+      <c r="D17" s="139"/>
+      <c r="E17" s="140"/>
       <c r="F17" s="76">
         <f>SUM(F10:F16)</f>
         <v>200</v>
@@ -15320,16 +15320,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A17:E17"/>
@@ -15339,6 +15329,16 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7 D18" xr:uid="{517DF1E8-3052-48CF-9AE1-C19E6ECB6686}">
@@ -15443,10 +15443,10 @@
         <v>81</v>
       </c>
       <c r="B11" s="117">
-        <v>46094</v>
+        <v>46155</v>
       </c>
       <c r="C11" s="117">
-        <v>46095</v>
+        <v>46156</v>
       </c>
       <c r="D11" s="87">
         <v>1</v>
@@ -16367,9 +16367,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16511,19 +16514,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76F64187-8300-4B72-BC78-4EA8CE42E92D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9098A285-2EB1-499B-BF89-1E169B414849}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -16547,9 +16546,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9098A285-2EB1-499B-BF89-1E169B414849}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76F64187-8300-4B72-BC78-4EA8CE42E92D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
